--- a/questionnaire_templates/013_evolutionary_process_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/013_evolutionary_process_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'1._evolution_is_the_scientifically_proven_fact_that_all_living_things_have_changed_over_time_through_genetic_variation_and_mutation.'}</t>
+          <t>1._evolution_is_the_scientifically_proven_fact_that_all_living_things_have_changed_over_time_through_genetic_variation_and_mutation.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': '1. Evolution is the scientifically proven fact that all living things have changed over time through genetic variation and mutation.'}</t>
+          <t>1. Evolution is the scientifically proven fact that all living things have changed over time through genetic variation and mutation.</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'2._evolutionary_change_can_occur_in_a_single_generation_or_over_many_generations.'}</t>
+          <t>2._evolutionary_change_can_occur_in_a_single_generation_or_over_many_generations.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': '2. Evolutionary change can occur in a single generation or over many generations.'}</t>
+          <t>2. Evolutionary change can occur in a single generation or over many generations.</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'3._evolutionary_change_is_driven_by_mutation,_genetic_drift,_gene_flow,_and_other_mechanisms.'}</t>
+          <t>3._evolutionary_change_is_driven_by_mutation,_genetic_drift,_gene_flow,_and_other_mechanisms.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': '3. Evolutionary change is driven by mutation, genetic drift, gene flow, and other mechanisms.'}</t>
+          <t>3. Evolutionary change is driven by mutation, genetic drift, gene flow, and other mechanisms.</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'4._evolutionary_change_is_the_only_way_to_account_for_the_origin_of_species.'}</t>
+          <t>4._evolutionary_change_is_the_only_way_to_account_for_the_origin_of_species.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': '4. Evolutionary change is the only way to account for the origin of species.'}</t>
+          <t>4. Evolutionary change is the only way to account for the origin of species.</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'5._evolutionary_change_can_occur_at_any_speed.'}</t>
+          <t>5._evolutionary_change_can_occur_at_any_speed.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': '5. Evolutionary change can occur at any speed.'}</t>
+          <t>5. Evolutionary change can occur at any speed.</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'6._all_species_have_changed_over_time.'}</t>
+          <t>6._all_species_have_changed_over_time.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': '6. All species have changed over time.'}</t>
+          <t>6. All species have changed over time.</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Neither agree nor disagree'}</t>
+          <t>Neither agree nor disagree</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'High school'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': "Master's degree"}</t>
+          <t>Master's degree</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_'ph.d.'}</t>
+          <t>ph.d.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': 'Ph.D.'}</t>
+          <t>Ph.D.</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
